--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1167"/>
+  <dimension ref="A1:C1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17777,6 +17777,215 @@
         <v>259</v>
       </c>
     </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr"/>
+      <c r="C1168" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr"/>
+      <c r="C1169" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr"/>
+      <c r="C1170" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr"/>
+      <c r="C1171" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr"/>
+      <c r="C1172" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr"/>
+      <c r="C1173" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr"/>
+      <c r="C1174" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr"/>
+      <c r="C1175" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr"/>
+      <c r="C1176" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr"/>
+      <c r="C1177" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr"/>
+      <c r="C1178" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr"/>
+      <c r="C1179" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr"/>
+      <c r="C1180" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr"/>
+      <c r="C1181" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr"/>
+      <c r="C1182" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr"/>
+      <c r="C1183" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr"/>
+      <c r="C1184" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr"/>
+      <c r="C1185" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr"/>
+      <c r="C1186" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1186"/>
+  <dimension ref="A1:C1287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17986,6 +17986,1117 @@
         <v>260</v>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr"/>
+      <c r="C1187" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr"/>
+      <c r="C1188" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr"/>
+      <c r="C1189" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr"/>
+      <c r="C1190" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr"/>
+      <c r="C1191" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr"/>
+      <c r="C1192" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr"/>
+      <c r="C1193" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr"/>
+      <c r="C1194" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr"/>
+      <c r="C1195" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr"/>
+      <c r="C1196" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr"/>
+      <c r="C1197" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr"/>
+      <c r="C1198" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr"/>
+      <c r="C1199" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr"/>
+      <c r="C1200" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr"/>
+      <c r="C1201" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr"/>
+      <c r="C1202" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr"/>
+      <c r="C1203" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr"/>
+      <c r="C1204" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr"/>
+      <c r="C1205" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr"/>
+      <c r="C1206" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr"/>
+      <c r="C1207" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr"/>
+      <c r="C1208" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr"/>
+      <c r="C1209" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr"/>
+      <c r="C1210" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr"/>
+      <c r="C1211" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr"/>
+      <c r="C1212" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr"/>
+      <c r="C1213" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr"/>
+      <c r="C1214" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr"/>
+      <c r="C1215" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr"/>
+      <c r="C1216" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr"/>
+      <c r="C1217" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr"/>
+      <c r="C1218" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr"/>
+      <c r="C1219" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr"/>
+      <c r="C1220" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr"/>
+      <c r="C1221" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr"/>
+      <c r="C1222" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr"/>
+      <c r="C1223" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr"/>
+      <c r="C1224" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr"/>
+      <c r="C1225" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr"/>
+      <c r="C1226" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr"/>
+      <c r="C1227" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr"/>
+      <c r="C1228" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr"/>
+      <c r="C1229" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr"/>
+      <c r="C1230" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr"/>
+      <c r="C1231" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr"/>
+      <c r="C1232" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr"/>
+      <c r="C1233" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr"/>
+      <c r="C1234" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr"/>
+      <c r="C1235" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr"/>
+      <c r="C1236" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr"/>
+      <c r="C1237" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr"/>
+      <c r="C1238" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr"/>
+      <c r="C1239" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr"/>
+      <c r="C1240" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr"/>
+      <c r="C1241" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr"/>
+      <c r="C1242" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr"/>
+      <c r="C1243" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr"/>
+      <c r="C1244" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr"/>
+      <c r="C1245" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr"/>
+      <c r="C1246" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr"/>
+      <c r="C1247" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr"/>
+      <c r="C1248" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr"/>
+      <c r="C1249" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr"/>
+      <c r="C1250" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr"/>
+      <c r="C1251" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr"/>
+      <c r="C1252" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr"/>
+      <c r="C1253" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr"/>
+      <c r="C1254" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr"/>
+      <c r="C1255" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr"/>
+      <c r="C1256" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr"/>
+      <c r="C1257" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr"/>
+      <c r="C1258" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr"/>
+      <c r="C1259" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr"/>
+      <c r="C1260" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr"/>
+      <c r="C1261" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr"/>
+      <c r="C1262" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr"/>
+      <c r="C1263" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr"/>
+      <c r="C1264" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr"/>
+      <c r="C1265" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr"/>
+      <c r="C1266" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr"/>
+      <c r="C1267" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr"/>
+      <c r="C1268" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr"/>
+      <c r="C1269" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr"/>
+      <c r="C1270" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr"/>
+      <c r="C1271" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr"/>
+      <c r="C1272" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr"/>
+      <c r="C1273" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr"/>
+      <c r="C1274" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr"/>
+      <c r="C1275" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr"/>
+      <c r="C1276" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr"/>
+      <c r="C1277" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr"/>
+      <c r="C1278" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr"/>
+      <c r="C1279" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr"/>
+      <c r="C1280" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr"/>
+      <c r="C1281" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr"/>
+      <c r="C1282" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr"/>
+      <c r="C1283" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr"/>
+      <c r="C1284" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr"/>
+      <c r="C1285" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr"/>
+      <c r="C1286" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr"/>
+      <c r="C1287" t="n">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1287"/>
+  <dimension ref="A1:C1304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19097,6 +19097,213 @@
         <v>264</v>
       </c>
     </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr"/>
+      <c r="C1288" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr"/>
+      <c r="C1289" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr"/>
+      <c r="C1290" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr"/>
+      <c r="C1291" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr"/>
+      <c r="C1292" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr"/>
+      <c r="C1297" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr"/>
+      <c r="C1298" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr"/>
+      <c r="C1299" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr"/>
+      <c r="C1300" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr"/>
+      <c r="C1301" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr"/>
+      <c r="C1302" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr"/>
+      <c r="C1303" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr"/>
+      <c r="C1304" t="n">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1304"/>
+  <dimension ref="A1:C1328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19304,6 +19304,283 @@
         <v>265</v>
       </c>
     </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr"/>
+      <c r="C1305" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr"/>
+      <c r="C1306" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr"/>
+      <c r="C1307" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr"/>
+      <c r="C1308" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr"/>
+      <c r="C1309" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr"/>
+      <c r="C1312" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr"/>
+      <c r="C1313" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr"/>
+      <c r="C1314" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr"/>
+      <c r="C1315" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr"/>
+      <c r="C1316" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr"/>
+      <c r="C1318" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr"/>
+      <c r="C1319" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr"/>
+      <c r="C1320" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr"/>
+      <c r="C1321" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr"/>
+      <c r="C1322" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr"/>
+      <c r="C1323" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr"/>
+      <c r="C1324" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr"/>
+      <c r="C1325" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr"/>
+      <c r="C1326" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr"/>
+      <c r="C1327" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr"/>
+      <c r="C1328" t="n">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1328"/>
+  <dimension ref="A1:C1333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19581,6 +19581,81 @@
         <v>267</v>
       </c>
     </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1333"/>
+  <dimension ref="A1:C1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16625,3035 +16625,46 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1065" t="inlineStr"/>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
       <c r="C1065" t="n">
-        <v>132</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1066" t="inlineStr"/>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
       <c r="C1066" t="n">
-        <v>132</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1067" t="inlineStr"/>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
       <c r="C1067" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1068" t="inlineStr"/>
-      <c r="C1068" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1069" t="inlineStr"/>
-      <c r="C1069" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1070" t="inlineStr"/>
-      <c r="C1070" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1071" t="inlineStr"/>
-      <c r="C1071" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1072" t="inlineStr"/>
-      <c r="C1072" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1073" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vanni sanna
-  sassari </t>
-        </is>
-      </c>
-      <c r="C1073" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1074" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio dei marmi
-  carrara </t>
-        </is>
-      </c>
-      <c r="C1074" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="B1075" t="inlineStr">
-        <is>
-          <t>UiGfvfvT</t>
-        </is>
-      </c>
-      <c r="C1075" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1076" t="inlineStr">
-        <is>
-          <t>tYVGfTo2</t>
-        </is>
-      </c>
-      <c r="C1076" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1077" t="inlineStr"/>
-      <c r="C1077" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1078" t="inlineStr">
-        <is>
-          <t>tYVGfTo2</t>
-        </is>
-      </c>
-      <c r="C1078" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1079" t="inlineStr"/>
-      <c r="C1079" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1080" t="inlineStr"/>
-      <c r="C1080" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1081" t="inlineStr"/>
-      <c r="C1081" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1082" t="inlineStr"/>
-      <c r="C1082" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1083" t="inlineStr"/>
-      <c r="C1083" t="n">
         <v>255</v>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1084" t="inlineStr"/>
-      <c r="C1084" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1085" t="inlineStr"/>
-      <c r="C1085" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1086" t="inlineStr"/>
-      <c r="C1086" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1087" t="inlineStr"/>
-      <c r="C1087" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1088" t="inlineStr"/>
-      <c r="C1088" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1089" t="inlineStr"/>
-      <c r="C1089" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1090" t="inlineStr"/>
-      <c r="C1090" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1091" t="inlineStr"/>
-      <c r="C1091" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1092" t="inlineStr"/>
-      <c r="C1092" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1093" t="inlineStr"/>
-      <c r="C1093" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1094" t="inlineStr"/>
-      <c r="C1094" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1095" t="inlineStr"/>
-      <c r="C1095" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1096" t="inlineStr"/>
-      <c r="C1096" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1097" t="inlineStr"/>
-      <c r="C1097" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1098" t="inlineStr"/>
-      <c r="C1098" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr"/>
-      <c r="C1099" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1100" t="inlineStr"/>
-      <c r="C1100" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1101" t="inlineStr"/>
-      <c r="C1101" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1102" t="inlineStr"/>
-      <c r="C1102" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1103" t="inlineStr"/>
-      <c r="C1103" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1104" t="inlineStr"/>
-      <c r="C1104" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1105" t="inlineStr"/>
-      <c r="C1105" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1106" t="inlineStr"/>
-      <c r="C1106" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr"/>
-      <c r="C1107" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1108" t="inlineStr"/>
-      <c r="C1108" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1109">
-      <c r="A1109" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1109" t="inlineStr"/>
-      <c r="C1109" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="1110">
-      <c r="A1110" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1110" t="inlineStr"/>
-      <c r="C1110" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1111">
-      <c r="A1111" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1111" t="inlineStr"/>
-      <c r="C1111" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1112">
-      <c r="A1112" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1112" t="inlineStr"/>
-      <c r="C1112" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1113">
-      <c r="A1113" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1113" t="inlineStr"/>
-      <c r="C1113" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1114">
-      <c r="A1114" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1114" t="inlineStr"/>
-      <c r="C1114" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1115">
-      <c r="A1115" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1115" t="inlineStr"/>
-      <c r="C1115" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1116" t="inlineStr"/>
-      <c r="C1116" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="1117">
-      <c r="A1117" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1117" t="inlineStr"/>
-      <c r="C1117" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="1118">
-      <c r="A1118" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1118" t="inlineStr"/>
-      <c r="C1118" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1119" t="inlineStr"/>
-      <c r="C1119" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1120" t="inlineStr"/>
-      <c r="C1120" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1121" t="inlineStr"/>
-      <c r="C1121" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1122" t="inlineStr"/>
-      <c r="C1122" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1123" t="inlineStr"/>
-      <c r="C1123" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1124" t="inlineStr"/>
-      <c r="C1124" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1125">
-      <c r="A1125" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1125" t="inlineStr"/>
-      <c r="C1125" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1126">
-      <c r="A1126" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1126" t="inlineStr"/>
-      <c r="C1126" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1127">
-      <c r="A1127" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1127" t="inlineStr"/>
-      <c r="C1127" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1128">
-      <c r="A1128" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1128" t="inlineStr"/>
-      <c r="C1128" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1129">
-      <c r="A1129" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1129" t="inlineStr"/>
-      <c r="C1129" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1130">
-      <c r="A1130" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1130" t="inlineStr"/>
-      <c r="C1130" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1131">
-      <c r="A1131" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1131" t="inlineStr"/>
-      <c r="C1131" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1132">
-      <c r="A1132" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1132" t="inlineStr"/>
-      <c r="C1132" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1133">
-      <c r="A1133" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1133" t="inlineStr"/>
-      <c r="C1133" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1134">
-      <c r="A1134" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1134" t="inlineStr"/>
-      <c r="C1134" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1135">
-      <c r="A1135" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1135" t="inlineStr"/>
-      <c r="C1135" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1136">
-      <c r="A1136" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1136" t="inlineStr"/>
-      <c r="C1136" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="1137">
-      <c r="A1137" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1137" t="inlineStr"/>
-      <c r="C1137" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="1138">
-      <c r="A1138" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1138" t="inlineStr"/>
-      <c r="C1138" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="1139">
-      <c r="A1139" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1139" t="inlineStr"/>
-      <c r="C1139" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="1140">
-      <c r="A1140" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1140" t="inlineStr"/>
-      <c r="C1140" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="1141">
-      <c r="A1141" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1141" t="inlineStr"/>
-      <c r="C1141" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1142">
-      <c r="A1142" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1142" t="inlineStr"/>
-      <c r="C1142" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1143">
-      <c r="A1143" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1143" t="inlineStr"/>
-      <c r="C1143" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1144">
-      <c r="A1144" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1144" t="inlineStr"/>
-      <c r="C1144" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1145">
-      <c r="A1145" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1145" t="inlineStr"/>
-      <c r="C1145" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1146">
-      <c r="A1146" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1146" t="inlineStr"/>
-      <c r="C1146" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1147">
-      <c r="A1147" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1147" t="inlineStr"/>
-      <c r="C1147" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1148">
-      <c r="A1148" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1148" t="inlineStr"/>
-      <c r="C1148" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1149">
-      <c r="A1149" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1149" t="inlineStr"/>
-      <c r="C1149" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1150">
-      <c r="A1150" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1150" t="inlineStr"/>
-      <c r="C1150" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1151">
-      <c r="A1151" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1151" t="inlineStr"/>
-      <c r="C1151" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1152">
-      <c r="A1152" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1152" t="inlineStr"/>
-      <c r="C1152" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1153">
-      <c r="A1153" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1153" t="inlineStr"/>
-      <c r="C1153" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1154">
-      <c r="A1154" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1154" t="inlineStr"/>
-      <c r="C1154" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1155">
-      <c r="A1155" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1155" t="inlineStr"/>
-      <c r="C1155" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1156" t="inlineStr"/>
-      <c r="C1156" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1157" t="inlineStr"/>
-      <c r="C1157" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1158" t="inlineStr"/>
-      <c r="C1158" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1159" t="inlineStr"/>
-      <c r="C1159" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1160" t="inlineStr"/>
-      <c r="C1160" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1161" t="inlineStr"/>
-      <c r="C1161" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1162" t="inlineStr"/>
-      <c r="C1162" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1163" t="inlineStr"/>
-      <c r="C1163" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1164" t="inlineStr"/>
-      <c r="C1164" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1165" t="inlineStr"/>
-      <c r="C1165" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1166" t="inlineStr"/>
-      <c r="C1166" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1167" t="inlineStr"/>
-      <c r="C1167" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1168" t="inlineStr"/>
-      <c r="C1168" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1169" t="inlineStr"/>
-      <c r="C1169" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1170" t="inlineStr"/>
-      <c r="C1170" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1171" t="inlineStr"/>
-      <c r="C1171" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1172" t="inlineStr"/>
-      <c r="C1172" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1173" t="inlineStr"/>
-      <c r="C1173" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1174" t="inlineStr"/>
-      <c r="C1174" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1175" t="inlineStr"/>
-      <c r="C1175" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1176" t="inlineStr"/>
-      <c r="C1176" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1177" t="inlineStr"/>
-      <c r="C1177" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1178" t="inlineStr"/>
-      <c r="C1178" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1179" t="inlineStr"/>
-      <c r="C1179" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1180" t="inlineStr"/>
-      <c r="C1180" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1181" t="inlineStr"/>
-      <c r="C1181" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1182" t="inlineStr"/>
-      <c r="C1182" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1183" t="inlineStr"/>
-      <c r="C1183" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1184" t="inlineStr"/>
-      <c r="C1184" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1185" t="inlineStr"/>
-      <c r="C1185" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1186" t="inlineStr"/>
-      <c r="C1186" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1187" t="inlineStr"/>
-      <c r="C1187" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1188" t="inlineStr"/>
-      <c r="C1188" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1189" t="inlineStr"/>
-      <c r="C1189" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1190" t="inlineStr"/>
-      <c r="C1190" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1191" t="inlineStr"/>
-      <c r="C1191" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1192" t="inlineStr"/>
-      <c r="C1192" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1193" t="inlineStr"/>
-      <c r="C1193" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1194" t="inlineStr"/>
-      <c r="C1194" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1195" t="inlineStr"/>
-      <c r="C1195" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1196" t="inlineStr"/>
-      <c r="C1196" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1197" t="inlineStr"/>
-      <c r="C1197" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1198" t="inlineStr"/>
-      <c r="C1198" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="B1199" t="inlineStr"/>
-      <c r="C1199" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
-        <is>
-          <t>id_team_away</t>
-        </is>
-      </c>
-      <c r="B1200" t="inlineStr"/>
-      <c r="C1200" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1201" t="inlineStr"/>
-      <c r="C1201" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1202" t="inlineStr"/>
-      <c r="C1202" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1203" t="inlineStr"/>
-      <c r="C1203" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1204" t="inlineStr"/>
-      <c r="C1204" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1205" t="inlineStr"/>
-      <c r="C1205" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1206" t="inlineStr"/>
-      <c r="C1206" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1207" t="inlineStr"/>
-      <c r="C1207" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1208" t="inlineStr"/>
-      <c r="C1208" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1209" t="inlineStr"/>
-      <c r="C1209" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1210" t="inlineStr"/>
-      <c r="C1210" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1211" t="inlineStr"/>
-      <c r="C1211" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1212" t="inlineStr"/>
-      <c r="C1212" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1213" t="inlineStr"/>
-      <c r="C1213" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1214" t="inlineStr"/>
-      <c r="C1214" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1215">
-      <c r="A1215" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1215" t="inlineStr"/>
-      <c r="C1215" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1216">
-      <c r="A1216" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1216" t="inlineStr"/>
-      <c r="C1216" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1217">
-      <c r="A1217" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1217" t="inlineStr"/>
-      <c r="C1217" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1218">
-      <c r="A1218" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1218" t="inlineStr"/>
-      <c r="C1218" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1219">
-      <c r="A1219" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1219" t="inlineStr"/>
-      <c r="C1219" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1220">
-      <c r="A1220" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1220" t="inlineStr"/>
-      <c r="C1220" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1221">
-      <c r="A1221" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1221" t="inlineStr"/>
-      <c r="C1221" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1222">
-      <c r="A1222" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1222" t="inlineStr"/>
-      <c r="C1222" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1223">
-      <c r="A1223" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1223" t="inlineStr"/>
-      <c r="C1223" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1224">
-      <c r="A1224" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1224" t="inlineStr"/>
-      <c r="C1224" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1225">
-      <c r="A1225" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1225" t="inlineStr"/>
-      <c r="C1225" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1226">
-      <c r="A1226" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1226" t="inlineStr"/>
-      <c r="C1226" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="1227">
-      <c r="A1227" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1227" t="inlineStr"/>
-      <c r="C1227" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="1228">
-      <c r="A1228" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1228" t="inlineStr"/>
-      <c r="C1228" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="1229">
-      <c r="A1229" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1229" t="inlineStr"/>
-      <c r="C1229" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1230">
-      <c r="A1230" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1230" t="inlineStr"/>
-      <c r="C1230" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1231">
-      <c r="A1231" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1231" t="inlineStr"/>
-      <c r="C1231" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1232">
-      <c r="A1232" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1232" t="inlineStr"/>
-      <c r="C1232" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1233">
-      <c r="A1233" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1233" t="inlineStr"/>
-      <c r="C1233" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1234">
-      <c r="A1234" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1234" t="inlineStr"/>
-      <c r="C1234" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1235">
-      <c r="A1235" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1235" t="inlineStr"/>
-      <c r="C1235" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1236">
-      <c r="A1236" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1236" t="inlineStr"/>
-      <c r="C1236" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1237">
-      <c r="A1237" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1237" t="inlineStr"/>
-      <c r="C1237" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1238">
-      <c r="A1238" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1238" t="inlineStr"/>
-      <c r="C1238" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1239">
-      <c r="A1239" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1239" t="inlineStr"/>
-      <c r="C1239" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="1240">
-      <c r="A1240" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1240" t="inlineStr"/>
-      <c r="C1240" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1241">
-      <c r="A1241" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1241" t="inlineStr"/>
-      <c r="C1241" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1242">
-      <c r="A1242" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1242" t="inlineStr"/>
-      <c r="C1242" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1243">
-      <c r="A1243" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1243" t="inlineStr"/>
-      <c r="C1243" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1244">
-      <c r="A1244" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1244" t="inlineStr"/>
-      <c r="C1244" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1245">
-      <c r="A1245" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1245" t="inlineStr"/>
-      <c r="C1245" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1246">
-      <c r="A1246" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1246" t="inlineStr"/>
-      <c r="C1246" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1247">
-      <c r="A1247" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1247" t="inlineStr"/>
-      <c r="C1247" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1248">
-      <c r="A1248" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1248" t="inlineStr"/>
-      <c r="C1248" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1249">
-      <c r="A1249" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1249" t="inlineStr"/>
-      <c r="C1249" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1250">
-      <c r="A1250" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1250" t="inlineStr"/>
-      <c r="C1250" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1251">
-      <c r="A1251" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1251" t="inlineStr"/>
-      <c r="C1251" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="1252">
-      <c r="A1252" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1252" t="inlineStr"/>
-      <c r="C1252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="1253">
-      <c r="A1253" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1253" t="inlineStr"/>
-      <c r="C1253" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="1254">
-      <c r="A1254" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1254" t="inlineStr"/>
-      <c r="C1254" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1255">
-      <c r="A1255" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1255" t="inlineStr"/>
-      <c r="C1255" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1256">
-      <c r="A1256" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1256" t="inlineStr"/>
-      <c r="C1256" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1257">
-      <c r="A1257" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1257" t="inlineStr"/>
-      <c r="C1257" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1258">
-      <c r="A1258" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1258" t="inlineStr"/>
-      <c r="C1258" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1259">
-      <c r="A1259" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1259" t="inlineStr"/>
-      <c r="C1259" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1260">
-      <c r="A1260" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1260" t="inlineStr"/>
-      <c r="C1260" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1261">
-      <c r="A1261" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1261" t="inlineStr"/>
-      <c r="C1261" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1262">
-      <c r="A1262" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1262" t="inlineStr"/>
-      <c r="C1262" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1263">
-      <c r="A1263" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1263" t="inlineStr"/>
-      <c r="C1263" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1264">
-      <c r="A1264" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1264" t="inlineStr"/>
-      <c r="C1264" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1265">
-      <c r="A1265" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1265" t="inlineStr"/>
-      <c r="C1265" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1266">
-      <c r="A1266" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1266" t="inlineStr"/>
-      <c r="C1266" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1267">
-      <c r="A1267" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1267" t="inlineStr"/>
-      <c r="C1267" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1268">
-      <c r="A1268" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1268" t="inlineStr"/>
-      <c r="C1268" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1269">
-      <c r="A1269" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1269" t="inlineStr"/>
-      <c r="C1269" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1270">
-      <c r="A1270" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1270" t="inlineStr"/>
-      <c r="C1270" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1271">
-      <c r="A1271" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1271" t="inlineStr"/>
-      <c r="C1271" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1272">
-      <c r="A1272" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1272" t="inlineStr"/>
-      <c r="C1272" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1273">
-      <c r="A1273" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1273" t="inlineStr"/>
-      <c r="C1273" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1274">
-      <c r="A1274" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1274" t="inlineStr"/>
-      <c r="C1274" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1275">
-      <c r="A1275" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1275" t="inlineStr"/>
-      <c r="C1275" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="1276">
-      <c r="A1276" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1276" t="inlineStr"/>
-      <c r="C1276" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="1277">
-      <c r="A1277" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1277" t="inlineStr"/>
-      <c r="C1277" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="1278">
-      <c r="A1278" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1278" t="inlineStr"/>
-      <c r="C1278" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1279">
-      <c r="A1279" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1279" t="inlineStr"/>
-      <c r="C1279" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1280">
-      <c r="A1280" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1280" t="inlineStr"/>
-      <c r="C1280" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1281">
-      <c r="A1281" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1281" t="inlineStr"/>
-      <c r="C1281" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1282">
-      <c r="A1282" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1282" t="inlineStr"/>
-      <c r="C1282" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1283">
-      <c r="A1283" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1283" t="inlineStr"/>
-      <c r="C1283" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1284">
-      <c r="A1284" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1284" t="inlineStr"/>
-      <c r="C1284" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1285">
-      <c r="A1285" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1285" t="inlineStr"/>
-      <c r="C1285" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1286">
-      <c r="A1286" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1286" t="inlineStr"/>
-      <c r="C1286" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1287">
-      <c r="A1287" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1287" t="inlineStr"/>
-      <c r="C1287" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="1288">
-      <c r="A1288" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1288" t="inlineStr"/>
-      <c r="C1288" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1289">
-      <c r="A1289" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1289" t="inlineStr"/>
-      <c r="C1289" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1290">
-      <c r="A1290" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1290" t="inlineStr"/>
-      <c r="C1290" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1291">
-      <c r="A1291" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1291" t="inlineStr"/>
-      <c r="C1291" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1292">
-      <c r="A1292" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1292" t="inlineStr"/>
-      <c r="C1292" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1293">
-      <c r="A1293" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena a 
-  ita </t>
-        </is>
-      </c>
-      <c r="C1293" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1294">
-      <c r="A1294" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">crezzini v 
-  ita </t>
-        </is>
-      </c>
-      <c r="C1294" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1295">
-      <c r="A1295" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">galipo s 
-  ita </t>
-        </is>
-      </c>
-      <c r="C1295" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1296">
-      <c r="A1296" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scatena g 
-  ita </t>
-        </is>
-      </c>
-      <c r="C1296" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="1297">
-      <c r="A1297" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1297" t="inlineStr"/>
-      <c r="C1297" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="1298">
-      <c r="A1298" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1298" t="inlineStr"/>
-      <c r="C1298" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1299">
-      <c r="A1299" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1299" t="inlineStr"/>
-      <c r="C1299" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1300">
-      <c r="A1300" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1300" t="inlineStr"/>
-      <c r="C1300" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1301">
-      <c r="A1301" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1301" t="inlineStr"/>
-      <c r="C1301" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1302">
-      <c r="A1302" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1302" t="inlineStr"/>
-      <c r="C1302" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1303">
-      <c r="A1303" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1303" t="inlineStr"/>
-      <c r="C1303" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1304">
-      <c r="A1304" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1304" t="inlineStr"/>
-      <c r="C1304" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="1305">
-      <c r="A1305" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1305" t="inlineStr"/>
-      <c r="C1305" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1306">
-      <c r="A1306" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1306" t="inlineStr"/>
-      <c r="C1306" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1307">
-      <c r="A1307" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1307" t="inlineStr"/>
-      <c r="C1307" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1308">
-      <c r="A1308" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1308" t="inlineStr"/>
-      <c r="C1308" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1309">
-      <c r="A1309" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1309" t="inlineStr"/>
-      <c r="C1309" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1310">
-      <c r="A1310" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">perri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="C1310" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="1311">
-      <c r="A1311" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1311" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="C1311" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="1312">
-      <c r="A1312" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1312" t="inlineStr"/>
-      <c r="C1312" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="1313">
-      <c r="A1313" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1313" t="inlineStr"/>
-      <c r="C1313" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1314">
-      <c r="A1314" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1314" t="inlineStr"/>
-      <c r="C1314" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1315">
-      <c r="A1315" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1315" t="inlineStr"/>
-      <c r="C1315" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1316">
-      <c r="A1316" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1316" t="inlineStr"/>
-      <c r="C1316" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1317">
-      <c r="A1317" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1317" t="inlineStr">
-        <is>
-          <t>WE57Jh0D</t>
-        </is>
-      </c>
-      <c r="C1317" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1318">
-      <c r="A1318" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1318" t="inlineStr"/>
-      <c r="C1318" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1319">
-      <c r="A1319" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1319" t="inlineStr"/>
-      <c r="C1319" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1320">
-      <c r="A1320" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1320" t="inlineStr"/>
-      <c r="C1320" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="1321">
-      <c r="A1321" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1321" t="inlineStr"/>
-      <c r="C1321" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="1322">
-      <c r="A1322" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1322" t="inlineStr"/>
-      <c r="C1322" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1323">
-      <c r="A1323" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1323" t="inlineStr"/>
-      <c r="C1323" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1324">
-      <c r="A1324" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1324" t="inlineStr"/>
-      <c r="C1324" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1325">
-      <c r="A1325" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1325" t="inlineStr"/>
-      <c r="C1325" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1326">
-      <c r="A1326" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1326" t="inlineStr"/>
-      <c r="C1326" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1327">
-      <c r="A1327" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1327" t="inlineStr"/>
-      <c r="C1327" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1328">
-      <c r="A1328" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1328" t="inlineStr"/>
-      <c r="C1328" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="1329">
-      <c r="A1329" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1329" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-      <c r="C1329" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="1330">
-      <c r="A1330" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1330" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-      <c r="C1330" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="1331">
-      <c r="A1331" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1331" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="C1331" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="1332">
-      <c r="A1332" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1332" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-      <c r="C1332" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="1333">
-      <c r="A1333" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1333" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-      <c r="C1333" t="n">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
